--- a/AI_Audit_Log_DE200075.xlsx
+++ b/AI_Audit_Log_DE200075.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Materials\SWP391\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092D5A95-A2B1-4C58-AF76-13A4A1CFBF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC153E8-DB46-4121-AAD5-058A06337621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Iter 1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -59,10 +59,27 @@
     <t>Process/Algorithm</t>
   </si>
   <si>
-    <t>(Thuật toán/Quy trình)</t>
-  </si>
-  <si>
-    <t>"Viết mã (Controller và DAO) thực hiện chức năng thêm, sửa, xóa, xem (CRUD) cho bảng Chuyên khoa (Department) dành cho module Admin."</t>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <r>
+      <t>[Department management]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "Viết các hàm API (CRUD) để Admin tạo, xem, cập nhật và xóa Chuyên khoa (Department)."</t>
+    </r>
   </si>
   <si>
     <r>
@@ -75,7 +92,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> AI cung cấp code xử lý CRUD kết nối thẳng database trong từng hàm.</t>
+      <t xml:space="preserve"> AI cung cấp cấu trúc code API rất chuẩn, chia sẵn các layer Controller và Service gọn gàng.</t>
     </r>
   </si>
   <si>
@@ -89,17 +106,40 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Tôi nhận thấy code của AI hoạt động được nhưng khó bảo trì. Tôi đã áp dụng kỹ thuật Pattern (Repository Pattern) tách riêng tầng xử lý dữ liệu và tầng điều khiển để code tuân thủ nguyên tắc S.O.L.I.D.</t>
-    </r>
-  </si>
-  <si>
-    <t>Evaluation</t>
-  </si>
-  <si>
-    <t>(Đánh giá/Sửa lỗi)</t>
-  </si>
-  <si>
-    <t>"Tạo chức năng cho Admin cập nhật thông tin bác sĩ (tên, năm sinh, số điện thoại, chuyên khoa)."</t>
+      <t xml:space="preserve"> Tôi đồng ý hoàn toàn với cấu trúc AI đưa ra vì nó đúng với best practice. Tôi giữ lại 95% code, chỉ tinh chỉnh (tweak) thêm annotation phân quyền </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>@PreAuthorize("hasRole('ADMIN')")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ở đầu mỗi hàm để đảm bảo tính bảo mật cho hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[Doctor management]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "Tạo form giao diện và logic kiểm tra lỗi (validation) khi Admin thêm mới thông tin bác sĩ."</t>
+    </r>
   </si>
   <si>
     <r>
@@ -112,7 +152,91 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> AI viết hàm cập nhật cơ bản </t>
+      <t xml:space="preserve"> AI sinh ra form giao diện rất đẹp và có sẵn các logic kiểm tra dữ liệu trống cơ bản.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Giao diện AI làm giúp tôi tiết kiệm rất nhiều thời gian, tôi áp dụng ngay. Ở phần validation, tôi chỉ bổ sung thêm một đoạn Regex nhỏ để bắt buộc trường "Số điện thoại" phải theo đúng định dạng 10 số của Việt Nam (bắt đầu bằng số 0).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[Patient management]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "Viết cấu hình phân quyền cho phép cả Role Lễ tân và Admin đều có quyền tạo và quản lý hồ sơ bệnh nhân."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất cấu hình phân quyền theo Role (Role-Based Access Control) cho phép 2 quyền truy cập cùng một endpoint API.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi nhận diện đây là một Pattern tiêu chuẩn và rất an toàn. Tôi áp dụng trực tiếp cách của AI, chỉ chuyển phần cấu hình này sang một file Security Config riêng biệt để code sạch sẽ và dễ quản lý hơn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[Staff management]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "Thiết kế Database để Admin quản lý các nhân viên: Lễ tân, Dược sĩ, Nhân viên xét nghiệm và Admin. Nên thiết kế như thế nào?"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AI gợi ý dùng chiến lược Single Table: Tạo chung 1 bảng </t>
     </r>
     <r>
       <rPr>
@@ -121,40 +245,84 @@
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
-      <t>UPDATE Doctor SET...</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> dựa trên dữ liệu đầu vào.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi đánh giá (Evaluate) đoạn code AI thiếu bước xác thực dữ liệu (Validation). Tôi đã tự bổ sung logic kiểm tra định dạng số điện thoại bằng Regex và bắt lỗi trùng lặp Email/Số điện thoại trước khi cho phép lưu xuống Database.</t>
-    </r>
-  </si>
-  <si>
-    <t>Abstraction</t>
-  </si>
-  <si>
-    <t>(Trừu tượng hóa)</t>
-  </si>
-  <si>
-    <t>"Viết logic phân quyền cho chức năng quản lý hồ sơ bệnh nhân, yêu cầu cả Role Lễ tân và Admin đều có quyền truy cập."</t>
+      <t>Users</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> và dùng cột </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Role</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (ENUM) để phân biệt các loại nhân viên thay vì tạo 4 bảng rời rạc.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Khả năng trừu tượng hóa (Abstraction) của AI rất tuyệt vời. Việc gộp bảng giúp truy vấn dữ liệu nhanh hơn hẳn. Tôi chấp nhận thiết kế này 100% và chỉ tự thêm một cột </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Active/Inactive) để dễ dàng khóa tài khoản nhân viên khi cần.</t>
+    </r>
+  </si>
+  <si>
+    <t>Evaluation / Security</t>
+  </si>
+  <si>
+    <r>
+      <t>[Patient profile page]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "Viết hàm xử lý ở Backend cho phép Bệnh nhân cập nhật hồ sơ cá nhân của họ."</t>
+    </r>
   </si>
   <si>
     <r>
@@ -167,7 +335,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> AI dùng cấu trúc điều kiện cứng: </t>
+      <t xml:space="preserve"> AI viết hàm cập nhật đúng logic, sử dụng </t>
     </r>
     <r>
       <rPr>
@@ -176,16 +344,16 @@
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
-      <t>if(user.role == "Admin" || user.role == "Receptionist")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> để chặn quyền.</t>
+      <t>PatientID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> truyền từ dưới Client (Giao diện) lên để tìm dữ liệu.</t>
     </r>
   </si>
   <si>
@@ -199,7 +367,52 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Tôi đánh giá cách hardcode này không linh hoạt (Oversimplification). Tôi đã áp dụng tính trừu tượng hóa, thay thế bằng Middleware/Filter hoặc Annotation </t>
+      <t xml:space="preserve"> Code của AI chạy tốt nhưng tôi nhận thấy có rủi ro bảo mật (người dùng có thể tự đổi ID). Tôi đã giữ lại toàn bộ logic xử lý dữ liệu của AI, chỉ sửa lại một chút là lấy ID trực tiếp từ Token đăng nhập trên Server thay vì lấy từ Client gửi lên.</t>
+    </r>
+  </si>
+  <si>
+    <t>Decomposition</t>
+  </si>
+  <si>
+    <r>
+      <t>[Doctor profile page]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "Tạo giao diện trang Profile cho Bác sĩ, hiển thị thông tin cá nhân và thông tin chuyên khoa tương ứng."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AI cung cấp một khối code UI hiển thị đầy đủ cả 2 thông tin rất chính xác và đẹp mắt.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Code giao diện AI làm rất tốt. Để dễ bảo trì sau này, tôi áp dụng kỹ thuật Phân rã (Decomposition): Cắt đoạn code của AI thành 2 Component nhỏ hơn là </t>
     </r>
     <r>
       <rPr>
@@ -208,39 +421,16 @@
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
-      <t>@RequireRole(Roles = {"Admin", "Receptionist"})</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> giúp quản lý quyền tập trung và dễ mở rộng.</t>
-    </r>
-  </si>
-  <si>
-    <t>Pattern Recognition</t>
-  </si>
-  <si>
-    <t>(Nhận diện mẫu)</t>
-  </si>
-  <si>
-    <t>"Thiết kế cơ sở dữ liệu để Admin quản lý các tài khoản: Lễ tân, Dược sĩ, Nhân viên xét nghiệm và Admin khác."</t>
-  </si>
-  <si>
-    <r>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> AI đề xuất tạo 4 bảng riêng biệt: </t>
+      <t>DoctorInfo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
     </r>
     <r>
       <rPr>
@@ -249,227 +439,16 @@
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
-      <t>Table_Receptionist</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table_Pharmacist</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table_LabTech</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table_Admin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Quyết định:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi nhận diện được cấu trúc lặp lại của dữ liệu (Pattern). Tôi đã thiết kế gom tất cả thành 1 bảng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>Users</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> chung (chứa Username, Password) và dùng cột </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>RoleID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> để phân biệt các loại nhân sự, giúp tối ưu truy vấn.</t>
-    </r>
-  </si>
-  <si>
-    <t>Security / Evaluation</t>
-  </si>
-  <si>
-    <t>(Đánh giá bảo mật)</t>
-  </si>
-  <si>
-    <t>"Viết API cho phép Bệnh nhân cập nhật thông tin hồ sơ cá nhân của mình."</t>
-  </si>
-  <si>
-    <r>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> AI viết API nhận tham số </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>PatientID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> từ giao diện (Client) gửi lên để tìm và cập nhật dữ liệu.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi phát hiện lỗi bảo mật nghiêm trọng (IDOR) vì user có thể sửa ID để đổi thông tin người khác. Tôi đã loại bỏ code AI, tự viết lại hàm lấy trực tiếp ID từ Token/Session đăng nhập bảo mật ở server.</t>
-    </r>
-  </si>
-  <si>
-    <t>(Tối ưu hiệu suất)</t>
-  </si>
-  <si>
-    <t>"Viết hàm lấy thông tin hồ sơ của một Bác sĩ kèm theo Tên Chuyên khoa mà bác sĩ đó đang công tác để hiển thị lên trang Profile."</t>
-  </si>
-  <si>
-    <r>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> AI viết 2 vòng lặp: Lấy danh sách bác sĩ, sau đó gọi thêm câu truy vấn phụ để tìm chuyên khoa tương ứng.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Giải pháp của AI gây ra lỗi hiệu suất N+1 Query. Tôi đã thiết kế lại thuật toán truy vấn, sử dụng một câu lệnh </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>SQL INNER JOIN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> duy nhất giữa bảng Bác sĩ và Chuyên khoa để tăng tốc độ load trang.</t>
+      <t>DepartmentInfo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> rồi gọi chúng vào trang chính.</t>
     </r>
   </si>
 </sst>
@@ -477,7 +456,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,13 +473,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
@@ -585,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -593,16 +565,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -615,15 +581,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -984,236 +941,230 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="29.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:5" ht="29.25" customHeight="1">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="87" thickBot="1">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="43.5" customHeight="1">
+      <c r="A6" s="6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" ht="87" thickBot="1">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="43.5" customHeight="1">
+      <c r="A10" s="6">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" ht="72.75" thickBot="1">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="43.5" customHeight="1">
+      <c r="A14" s="6">
+        <v>4</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="9"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="9"/>
-      <c r="B4" s="5" t="s">
+      <c r="C14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" ht="87" thickBot="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="43.5" customHeight="1">
+      <c r="A18" s="6">
         <v>5</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" ht="72.75" thickBot="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="43.5">
-      <c r="A6" s="8">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="9"/>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" ht="87" thickBot="1">
-      <c r="A9" s="10"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="43.5">
-      <c r="A10" s="8">
-        <v>3</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="9"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="9"/>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="101.25" thickBot="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="43.5">
-      <c r="A14" s="8">
-        <v>4</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="B18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="9"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="9"/>
-      <c r="B16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" ht="72.75" thickBot="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="7" t="s">
+    <row r="19" spans="1:4">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" ht="87" thickBot="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="43.5">
-      <c r="A18" s="8">
-        <v>5</v>
-      </c>
-      <c r="B18" s="3" t="s">
+    <row r="22" spans="1:4" ht="43.5" customHeight="1">
+      <c r="A22" s="6">
+        <v>6</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="3" t="s">
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" ht="72.75" thickBot="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="9"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="9"/>
-      <c r="B20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4" ht="72.75" thickBot="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="43.5">
-      <c r="A22" s="8">
-        <v>6</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="9"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="9"/>
-      <c r="B24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:4" ht="72.75" thickBot="1">
-      <c r="A25" s="10"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="C14:C17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="C18:C21"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="C22:C25"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B22:B25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
